--- a/Scripts/Race and Class Masks.xlsx
+++ b/Scripts/Race and Class Masks.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Games\ChromieCraft_3.3.5a\Custom Tools\Zeppelin-Core\Scripts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\wow-server\Zeppelin-Craft\Scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A5D3048-0BA6-4197-9A29-79C776C61939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A8B630F-92BD-4376-AED3-22AA5EFECE36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23040" yWindow="0" windowWidth="23040" windowHeight="12660" activeTab="2" xr2:uid="{4BBDA68F-2F2D-4AF6-AB25-AE65BDBBC453}"/>
+    <workbookView minimized="1" xWindow="23388" yWindow="5820" windowWidth="22020" windowHeight="18516" firstSheet="1" activeTab="1" xr2:uid="{4BBDA68F-2F2D-4AF6-AB25-AE65BDBBC453}"/>
   </bookViews>
   <sheets>
     <sheet name="Race Mask" sheetId="1" r:id="rId1"/>
-    <sheet name="Weapon Class Mask" sheetId="2" r:id="rId2"/>
-    <sheet name="Race Class Starting Skills" sheetId="3" r:id="rId3"/>
+    <sheet name="Class Mask" sheetId="4" r:id="rId2"/>
+    <sheet name="Weapon Class Mask" sheetId="2" r:id="rId3"/>
+    <sheet name="Race Class Starting Skills" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Weapon Class Mask'!$A$3:$B$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Weapon Class Mask'!$A$3:$B$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="78">
   <si>
     <t>HUMAN</t>
   </si>
@@ -270,6 +271,9 @@
   </si>
   <si>
     <t>Class Race - Starting Skill - Dagger - 173</t>
+  </si>
+  <si>
+    <t>Class</t>
   </si>
 </sst>
 </file>
@@ -1022,6 +1026,187 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8679B914-D9A6-4EB5-9EF9-E6C90370F93E}">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="1">
+        <f>IF(NOT(ISBLANK(C2)),POWER(2,B2-1),0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1">
+        <f t="shared" ref="D3:D11" si="0">IF(NOT(ISBLANK(C3)),POWER(2,B3-1),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="1">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="1">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="1">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="1">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="1">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="1">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="1">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="1">
+        <v>7</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="1">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="1">
+        <v>8</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="1">
+        <v>9</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="1">
+        <v>10</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="1">
+        <f>SUM(D2:D11)</f>
+        <v>109</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A12:C12"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EA75A47-7F84-4837-99EA-E1E053D382AD}">
   <dimension ref="A1:M20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1719,7 +1904,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDA85B2D-5CB3-4AA7-9E81-14CDAC14B018}">
   <dimension ref="A1:N304"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8150,6 +8335,15 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A238:K238"/>
+    <mergeCell ref="A255:K255"/>
+    <mergeCell ref="A272:K272"/>
+    <mergeCell ref="A289:K289"/>
+    <mergeCell ref="A153:K153"/>
+    <mergeCell ref="A170:K170"/>
+    <mergeCell ref="A187:K187"/>
+    <mergeCell ref="A204:K204"/>
+    <mergeCell ref="A221:K221"/>
     <mergeCell ref="A85:K85"/>
     <mergeCell ref="A102:K102"/>
     <mergeCell ref="A119:K119"/>
@@ -8159,15 +8353,6 @@
     <mergeCell ref="A17:K17"/>
     <mergeCell ref="A34:K34"/>
     <mergeCell ref="A51:K51"/>
-    <mergeCell ref="A238:K238"/>
-    <mergeCell ref="A255:K255"/>
-    <mergeCell ref="A272:K272"/>
-    <mergeCell ref="A289:K289"/>
-    <mergeCell ref="A153:K153"/>
-    <mergeCell ref="A170:K170"/>
-    <mergeCell ref="A187:K187"/>
-    <mergeCell ref="A204:K204"/>
-    <mergeCell ref="A221:K221"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
